--- a/Data Files/2.2. Send Request to Proxy Management Inquiry - Different Phone number.xlsx
+++ b/Data Files/2.2. Send Request to Proxy Management Inquiry - Different Phone number.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wirafidi/git/Bifast-2.0-Katalon/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C661D1E-7E57-4684-87DD-1E4AD36A1231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A354DE6D-E3B5-4442-BA14-C9C10AB75A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
   <sheets>
     <sheet name="PROXY" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Content_Type</t>
   </si>
@@ -33,33 +33,15 @@
     <t>transactionId</t>
   </si>
   <si>
-    <t>transactionCode</t>
-  </si>
-  <si>
-    <t>cid</t>
-  </si>
-  <si>
     <t>channelType</t>
   </si>
   <si>
     <t>application/json</t>
   </si>
   <si>
-    <t>FAST-JSON-MBL-03</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
     <t>proxyAlias</t>
   </si>
   <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
     <t>customerAccountNumber</t>
   </si>
   <si>
@@ -72,31 +54,34 @@
     <t>customerSecondaryType</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>customerSecondaryValue</t>
   </si>
   <si>
     <t>3273182301870002</t>
   </si>
   <si>
-    <t>Basic QWRtaW5pc3RyYXRvcjptYW5hZ2U=</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
-    <t>628213520061</t>
-  </si>
-  <si>
     <t>PORT</t>
   </si>
   <si>
-    <t>0019845621103</t>
-  </si>
-  <si>
-    <t>250820042320</t>
+    <t>0019845621101</t>
+  </si>
+  <si>
+    <t>62821528061</t>
+  </si>
+  <si>
+    <t>KOMIMOBILE</t>
+  </si>
+  <si>
+    <t>institutionBic</t>
+  </si>
+  <si>
+    <t>BMRIIDJA</t>
+  </si>
+  <si>
+    <t>250820049940</t>
   </si>
 </sst>
 </file>
@@ -203,9 +188,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -243,7 +228,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -349,7 +334,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -491,7 +476,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -499,91 +484,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAC831-256C-49B0-B0F6-AAF164E4E88A}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="12" width="20.21875" customWidth="1"/>
+    <col min="1" max="10" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="ANANDAAMELIA11@GMAIL.COM" xr:uid="{3B7A8BBE-E0F3-46DC-9F46-3243D7371273}"/>
+    <hyperlink ref="F2" r:id="rId1" display="ANANDAAMELIA11@GMAIL.COM" xr:uid="{3B7A8BBE-E0F3-46DC-9F46-3243D7371273}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
